--- a/models/builds/2026-05-10-coca-cola-financials.xlsx
+++ b/models/builds/2026-05-10-coca-cola-financials.xlsx
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:C41"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="52" min="1" max="1"/>
@@ -932,10 +932,12 @@
     <col width="2" customWidth="1" style="52" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="7.5" customHeight="1" s="53">
       <c r="B2" s="54" t="n"/>
       <c r="C2" s="54" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="14.25" customHeight="1" s="53">
       <c r="B4" s="55" t="inlineStr">
         <is>
@@ -961,6 +963,7 @@
       <c r="B7" s="58" t="n"/>
       <c r="C7" s="58" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="53">
       <c r="B9" s="59" t="inlineStr">
         <is>
@@ -1040,6 +1043,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="19.5" customHeight="1" s="53">
       <c r="B17" s="59" t="inlineStr">
         <is>
@@ -1107,6 +1111,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="19.5" customHeight="1" s="53">
       <c r="B24" s="59" t="inlineStr">
         <is>
@@ -1222,6 +1227,8 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36" ht="19.5" customHeight="1" s="53">
       <c r="B36" s="59" t="inlineStr">
         <is>
@@ -1253,10 +1260,139 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41" ht="20.25" customHeight="1" s="53">
       <c r="B41" s="71" t="inlineStr">
         <is>
           <t>Prepared per UH Mānoa brand standards (docs/_branding/design.json). Primary green #024731 · Open Sans typography · ADA-compliant contrast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>── Student Documentation ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nguyen Bui Ngoc Linh</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BUS-629 VEMBA International Corporate Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company (KO: NYSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Reporting Standard</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>U.S. GAAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Currency &amp; Units</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USD, figures in $millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fiscal Year (current)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FY2025 (January 1 – December 31, 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fiscal Year (prior)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FY2024 (January 1 – December 31, 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Source 10-K URL</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0000021344&amp;type=10-K&amp;dateb=&amp;owner=include&amp;count=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supplemental Data</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mergent 5-Year Financial Summary (accessed May 10, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Non-U.S. Adjustments</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>None — U.S. domestic issuer reporting in USD under U.S. GAAP</t>
         </is>
       </c>
     </row>
@@ -1898,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="52" min="1" max="1"/>
@@ -1907,6 +2043,7 @@
     <col width="24" customWidth="1" style="52" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22.5" customHeight="1" s="53">
       <c r="B2" s="72" t="inlineStr">
         <is>
@@ -1921,6 +2058,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="B5" s="81" t="inlineStr">
         <is>
@@ -2233,6 +2371,42 @@
         <v/>
       </c>
       <c r="D32" s="73" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Reconciliation note</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Template-computed CFO: $5,181M</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Reported CFO (10-K)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>$7,408M (FY2025 Coca-Cola 10-K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Difference: $2,227M</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Attributable to non-cash items not captured in template (stock-based compensation, deferred taxes, net pension adjustments, other operating items). Template uses simplified NI + D&amp;A + 5 working-capital lines only.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3475,7 +3649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:C24"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3.91" customWidth="1" style="52" min="1" max="1"/>
@@ -3483,6 +3657,7 @@
     <col width="70" customWidth="1" style="52" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22.5" customHeight="1" s="53">
       <c r="B2" s="72" t="inlineStr">
         <is>
@@ -3490,6 +3665,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="14.25" customHeight="1" s="53">
       <c r="B4" s="103" t="inlineStr">
         <is>
@@ -3558,7 +3734,7 @@
       </c>
       <c r="C9" s="61" t="inlineStr">
         <is>
-          <t>Mergent 5-Year Data + SEC EDGAR 10-K FY2025 (ko-20251231.htm)</t>
+          <t>Mergent 5-Year Financial Summary (accessed 2026-05-10) + SEC EDGAR 10-K FY2025; URL: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0000021344&amp;type=10-K&amp;dateb=&amp;owner=include&amp;count=10</t>
         </is>
       </c>
     </row>
@@ -3622,6 +3798,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="14.25" customHeight="1" s="53">
       <c r="B16" s="103" t="inlineStr">
         <is>
@@ -3682,6 +3859,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="14.25" customHeight="1" s="53">
       <c r="B22" s="103" t="inlineStr">
         <is>
